--- a/education_surveys/007_student_media_network_feedback--education_surveys.xlsx
+++ b/education_surveys/007_student_media_network_feedback--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1110,8 +1110,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="37" customWidth="1" min="2" max="2"/>
-    <col width="37" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'wujoy'}</t>
+          <t>wujoy</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'WUJOY'}</t>
+          <t>WUJOY</t>
         </is>
       </c>
     </row>
@@ -1156,12 +1156,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_89.9}</t>
+          <t>89.9</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 89.9}</t>
+          <t>89.9</t>
         </is>
       </c>
     </row>
@@ -1173,12 +1173,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'wrfl'}</t>
+          <t>wrfl</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'WRFL'}</t>
+          <t>WRFL</t>
         </is>
       </c>
     </row>
@@ -1190,12 +1190,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'daily'}</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Daily'}</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
@@ -1207,12 +1207,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'weekly'}</t>
+          <t>weekly</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Weekly'}</t>
+          <t>Weekly</t>
         </is>
       </c>
     </row>
@@ -1224,12 +1224,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1241,12 +1241,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'local_news'}</t>
+          <t>local_news</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Local News'}</t>
+          <t>Local News</t>
         </is>
       </c>
     </row>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'national_news'}</t>
+          <t>national_news</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'National News'}</t>
+          <t>National News</t>
         </is>
       </c>
     </row>
@@ -1275,12 +1275,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'entertainment_news'}</t>
+          <t>entertainment_news</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Entertainment News'}</t>
+          <t>Entertainment News</t>
         </is>
       </c>
     </row>
@@ -1292,12 +1292,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'facebook'}</t>
+          <t>facebook</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Facebook'}</t>
+          <t>Facebook</t>
         </is>
       </c>
     </row>
@@ -1309,12 +1309,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'instagram'}</t>
+          <t>instagram</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Instagram'}</t>
+          <t>Instagram</t>
         </is>
       </c>
     </row>
@@ -1326,12 +1326,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'twitter'}</t>
+          <t>twitter</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Twitter'}</t>
+          <t>Twitter</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'often'}</t>
+          <t>often</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Often'}</t>
+          <t>Often</t>
         </is>
       </c>
     </row>
@@ -1360,12 +1360,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -1377,12 +1377,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -1394,12 +1394,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'local_podcasts'}</t>
+          <t>local_podcasts</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Local Podcasts'}</t>
+          <t>Local Podcasts</t>
         </is>
       </c>
     </row>
@@ -1411,12 +1411,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'national_podcasts'}</t>
+          <t>national_podcasts</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'National Podcasts'}</t>
+          <t>National Podcasts</t>
         </is>
       </c>
     </row>
@@ -1428,12 +1428,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'entertainment_podcasts'}</t>
+          <t>entertainment_podcasts</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Entertainment Podcasts'}</t>
+          <t>Entertainment Podcasts</t>
         </is>
       </c>
     </row>
